--- a/DataTables/Datas/#VSCharacter.xlsx
+++ b/DataTables/Datas/#VSCharacter.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,6 +454,11 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>magnetRadius</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>startWeaponId</t>
         </is>
       </c>
@@ -496,6 +501,11 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>int</t>
         </is>
       </c>
@@ -537,6 +547,11 @@
         </is>
       </c>
       <c r="H3" t="inlineStr">
+        <is>
+          <t>磁吸半径(基础,被动 Magnet 加成叠加)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>初始武器id</t>
         </is>
@@ -564,6 +579,9 @@
         <v>0.4</v>
       </c>
       <c r="H4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" t="n">
         <v>1</v>
       </c>
     </row>
